--- a/3_ml_model/data/datasheets/PRISM_substrate_features_smiles.xlsx
+++ b/3_ml_model/data/datasheets/PRISM_substrate_features_smiles.xlsx
@@ -725,8 +725,6 @@
           <t>aromatic</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>0</v>
       </c>
@@ -841,12 +839,6 @@
       <c r="AS2" t="n">
         <v>0.1505</v>
       </c>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
@@ -889,8 +881,6 @@
           <t>aromatic</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>0</v>
       </c>
@@ -1005,12 +995,6 @@
       <c r="AS3" t="n">
         <v>0.1365</v>
       </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
@@ -1053,8 +1037,6 @@
           <t>aromatic</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>0</v>
       </c>
@@ -1169,12 +1151,6 @@
       <c r="AS4" t="n">
         <v>0.104</v>
       </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
@@ -1217,8 +1193,6 @@
           <t>aromatic</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>0</v>
       </c>
@@ -1333,12 +1307,6 @@
       <c r="AS5" t="n">
         <v>0.1545</v>
       </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
@@ -1381,8 +1349,6 @@
           <t>aromatic</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>0</v>
       </c>
@@ -1497,12 +1463,6 @@
       <c r="AS6" t="n">
         <v>0.1385</v>
       </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
@@ -1545,8 +1505,6 @@
           <t>aromatic</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>0</v>
       </c>
@@ -1661,12 +1619,6 @@
       <c r="AS7" t="n">
         <v>0.0915</v>
       </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="inlineStr"/>
-      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
@@ -1709,8 +1661,6 @@
           <t>hetero</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>0</v>
       </c>
@@ -1825,12 +1775,6 @@
       <c r="AS8" t="n">
         <v>0.114</v>
       </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr"/>
-      <c r="AX8" t="inlineStr"/>
-      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
@@ -1873,8 +1817,6 @@
           <t>aromatic</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>0</v>
       </c>
@@ -1989,12 +1931,6 @@
       <c r="AS9" t="n">
         <v>0.08450000000000001</v>
       </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="inlineStr"/>
-      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
@@ -2037,8 +1973,6 @@
           <t>aromatic</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>0</v>
       </c>
@@ -2153,12 +2087,6 @@
       <c r="AS10" t="n">
         <v>0.1195</v>
       </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr"/>
-      <c r="AX10" t="inlineStr"/>
-      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
@@ -2201,8 +2129,6 @@
           <t>aliphatic</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>0</v>
       </c>
@@ -2317,12 +2243,6 @@
       <c r="AS11" t="n">
         <v>0.144</v>
       </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr"/>
-      <c r="AX11" t="inlineStr"/>
-      <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
@@ -2365,8 +2285,6 @@
           <t>aliphatic</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>2</v>
       </c>
@@ -2481,12 +2399,6 @@
       <c r="AS12" t="n">
         <v>0.1115</v>
       </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AU12" t="inlineStr"/>
-      <c r="AV12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr"/>
-      <c r="AX12" t="inlineStr"/>
-      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="n">
         <v>79.62838201191815</v>
       </c>
@@ -2529,8 +2441,6 @@
           <t>aromatic</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>0</v>
       </c>
@@ -2645,12 +2555,6 @@
       <c r="AS13" t="n">
         <v>0.1255</v>
       </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AU13" t="inlineStr"/>
-      <c r="AV13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr"/>
-      <c r="AX13" t="inlineStr"/>
-      <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
@@ -2693,8 +2597,6 @@
           <t>aliphatic</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>2</v>
       </c>
@@ -2809,12 +2711,6 @@
       <c r="AS14" t="n">
         <v>0.08349999999999999</v>
       </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AU14" t="inlineStr"/>
-      <c r="AV14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr"/>
-      <c r="AX14" t="inlineStr"/>
-      <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="n">
         <v>84.75070005723813</v>
       </c>
@@ -2857,8 +2753,6 @@
           <t>aliphatic</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>3</v>
       </c>
@@ -2973,12 +2867,6 @@
       <c r="AS15" t="n">
         <v>0.204</v>
       </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AU15" t="inlineStr"/>
-      <c r="AV15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr"/>
-      <c r="AX15" t="inlineStr"/>
-      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="n">
         <v>56.34253510199881</v>
       </c>
@@ -3021,8 +2909,6 @@
           <t>aromatic</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>0</v>
       </c>
@@ -3137,12 +3023,6 @@
       <c r="AS16" t="n">
         <v>0.1475</v>
       </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AU16" t="inlineStr"/>
-      <c r="AV16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr"/>
-      <c r="AX16" t="inlineStr"/>
-      <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="n">
         <v>0</v>
       </c>
@@ -3185,8 +3065,6 @@
           <t>aromatic</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>0</v>
       </c>
@@ -3301,12 +3179,6 @@
       <c r="AS17" t="n">
         <v>0.081</v>
       </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AU17" t="inlineStr"/>
-      <c r="AV17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr"/>
-      <c r="AX17" t="inlineStr"/>
-      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
@@ -3349,8 +3221,6 @@
           <t>aromatic</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>0</v>
       </c>
@@ -3465,12 +3335,6 @@
       <c r="AS18" t="n">
         <v>0.1085</v>
       </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AU18" t="inlineStr"/>
-      <c r="AV18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr"/>
-      <c r="AX18" t="inlineStr"/>
-      <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
@@ -3513,8 +3377,6 @@
           <t>aromatic</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>0</v>
       </c>
@@ -3629,12 +3491,6 @@
       <c r="AS19" t="n">
         <v>0.1315</v>
       </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AU19" t="inlineStr"/>
-      <c r="AV19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr"/>
-      <c r="AX19" t="inlineStr"/>
-      <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
@@ -3677,8 +3533,6 @@
           <t>aromatic</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>0</v>
       </c>
@@ -3793,12 +3647,6 @@
       <c r="AS20" t="n">
         <v>0.09949999999999999</v>
       </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AU20" t="inlineStr"/>
-      <c r="AV20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr"/>
-      <c r="AX20" t="inlineStr"/>
-      <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="n">
         <v>0</v>
       </c>
@@ -3841,8 +3689,6 @@
           <t>hetero</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>0</v>
       </c>
@@ -3957,12 +3803,6 @@
       <c r="AS21" t="n">
         <v>0.183</v>
       </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AU21" t="inlineStr"/>
-      <c r="AV21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr"/>
-      <c r="AX21" t="inlineStr"/>
-      <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="n">
         <v>0</v>
       </c>
@@ -4005,8 +3845,6 @@
           <t>mixture</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>1</v>
       </c>
@@ -4121,12 +3959,6 @@
       <c r="AS22" t="n">
         <v>0.082</v>
       </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AU22" t="inlineStr"/>
-      <c r="AV22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr"/>
-      <c r="AX22" t="inlineStr"/>
-      <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="n">
         <v>105.2734411874615</v>
       </c>
@@ -4169,8 +4001,6 @@
           <t>aliphatic</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>1</v>
       </c>
@@ -4285,12 +4115,6 @@
       <c r="AS23" t="n">
         <v>0.08550000000000001</v>
       </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AU23" t="inlineStr"/>
-      <c r="AV23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr"/>
-      <c r="AX23" t="inlineStr"/>
-      <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="n">
         <v>103.523642700515</v>
       </c>
@@ -4333,8 +4157,6 @@
           <t>aromatic</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>0</v>
       </c>
@@ -4449,12 +4271,6 @@
       <c r="AS24" t="n">
         <v>0.108</v>
       </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AU24" t="inlineStr"/>
-      <c r="AV24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr"/>
-      <c r="AX24" t="inlineStr"/>
-      <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="n">
         <v>0</v>
       </c>
@@ -4497,8 +4313,6 @@
           <t>aromatic</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>0</v>
       </c>
@@ -4613,12 +4427,6 @@
       <c r="AS25" t="n">
         <v>0.116</v>
       </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AU25" t="inlineStr"/>
-      <c r="AV25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr"/>
-      <c r="AX25" t="inlineStr"/>
-      <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="n">
         <v>0</v>
       </c>
@@ -4661,8 +4469,6 @@
           <t>aliphatic</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>2</v>
       </c>
@@ -4777,12 +4583,6 @@
       <c r="AS26" t="n">
         <v>0.0575</v>
       </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AU26" t="inlineStr"/>
-      <c r="AV26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr"/>
-      <c r="AX26" t="inlineStr"/>
-      <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="n">
         <v>93.51172039549701</v>
       </c>
@@ -4825,8 +4625,6 @@
           <t>aliphatic</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>1</v>
       </c>
@@ -4941,12 +4739,6 @@
       <c r="AS27" t="n">
         <v>0.141</v>
       </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AU27" t="inlineStr"/>
-      <c r="AV27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr"/>
-      <c r="AX27" t="inlineStr"/>
-      <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="n">
         <v>81.70293389408093</v>
       </c>
@@ -4989,8 +4781,6 @@
           <t>mixture</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>1</v>
       </c>
@@ -5105,12 +4895,6 @@
       <c r="AS28" t="n">
         <v>0.125</v>
       </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AU28" t="inlineStr"/>
-      <c r="AV28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr"/>
-      <c r="AX28" t="inlineStr"/>
-      <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="n">
         <v>85.24541295880758</v>
       </c>
@@ -5153,8 +4937,6 @@
           <t>aromatic</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>0</v>
       </c>
@@ -5269,12 +5051,6 @@
       <c r="AS29" t="n">
         <v>0.126</v>
       </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AU29" t="inlineStr"/>
-      <c r="AV29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr"/>
-      <c r="AX29" t="inlineStr"/>
-      <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="n">
         <v>0</v>
       </c>
@@ -5317,8 +5093,6 @@
           <t>aromatic</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>0</v>
       </c>
@@ -5433,12 +5207,6 @@
       <c r="AS30" t="n">
         <v>0.068</v>
       </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AU30" t="inlineStr"/>
-      <c r="AV30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr"/>
-      <c r="AX30" t="inlineStr"/>
-      <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="n">
         <v>0</v>
       </c>
@@ -5481,8 +5249,6 @@
           <t>aromatic</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>0</v>
       </c>
@@ -5597,12 +5363,6 @@
       <c r="AS31" t="n">
         <v>0.1255</v>
       </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AU31" t="inlineStr"/>
-      <c r="AV31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr"/>
-      <c r="AX31" t="inlineStr"/>
-      <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="n">
         <v>0</v>
       </c>
@@ -5645,8 +5405,6 @@
           <t>aliphatic</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>0</v>
       </c>
@@ -5761,12 +5519,6 @@
       <c r="AS32" t="n">
         <v>0.07400000000000001</v>
       </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AU32" t="inlineStr"/>
-      <c r="AV32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr"/>
-      <c r="AX32" t="inlineStr"/>
-      <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="n">
         <v>0</v>
       </c>
@@ -5809,8 +5561,6 @@
           <t>aliphatic</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>2</v>
       </c>
@@ -5925,12 +5675,6 @@
       <c r="AS33" t="n">
         <v>0.094</v>
       </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AU33" t="inlineStr"/>
-      <c r="AV33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr"/>
-      <c r="AX33" t="inlineStr"/>
-      <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="n">
         <v>81.37713459421013</v>
       </c>
@@ -5973,8 +5717,6 @@
           <t>aliphatic</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>1</v>
       </c>
@@ -6089,12 +5831,6 @@
       <c r="AS34" t="n">
         <v>0.107</v>
       </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AU34" t="inlineStr"/>
-      <c r="AV34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr"/>
-      <c r="AX34" t="inlineStr"/>
-      <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="n">
         <v>103.005919896547</v>
       </c>
@@ -6137,8 +5873,6 @@
           <t>aromatic</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>0</v>
       </c>
@@ -6253,12 +5987,6 @@
       <c r="AS35" t="n">
         <v>0.136</v>
       </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AU35" t="inlineStr"/>
-      <c r="AV35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr"/>
-      <c r="AX35" t="inlineStr"/>
-      <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="n">
         <v>0</v>
       </c>
@@ -6301,8 +6029,6 @@
           <t>aliphatic</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>2</v>
       </c>
@@ -6417,12 +6143,6 @@
       <c r="AS36" t="n">
         <v>0.089</v>
       </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AU36" t="inlineStr"/>
-      <c r="AV36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr"/>
-      <c r="AX36" t="inlineStr"/>
-      <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="n">
         <v>85.15651106317671</v>
       </c>
@@ -6465,8 +6185,6 @@
           <t>aliphatic</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>1</v>
       </c>
@@ -6581,12 +6299,6 @@
       <c r="AS37" t="n">
         <v>0.096</v>
       </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AU37" t="inlineStr"/>
-      <c r="AV37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr"/>
-      <c r="AX37" t="inlineStr"/>
-      <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="n">
         <v>84.39090885609671</v>
       </c>
@@ -6629,8 +6341,6 @@
           <t>aromatic</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>0</v>
       </c>
@@ -6745,12 +6455,6 @@
       <c r="AS38" t="n">
         <v>0.134</v>
       </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AU38" t="inlineStr"/>
-      <c r="AV38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr"/>
-      <c r="AX38" t="inlineStr"/>
-      <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="n">
         <v>0</v>
       </c>
@@ -6793,8 +6497,6 @@
           <t>aromatic</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>0</v>
       </c>
@@ -6909,12 +6611,6 @@
       <c r="AS39" t="n">
         <v>0.116</v>
       </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AU39" t="inlineStr"/>
-      <c r="AV39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr"/>
-      <c r="AX39" t="inlineStr"/>
-      <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="n">
         <v>0</v>
       </c>
@@ -6957,8 +6653,6 @@
           <t>aromatic</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>0</v>
       </c>
@@ -7073,12 +6767,6 @@
       <c r="AS40" t="n">
         <v>0.09000000000000001</v>
       </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AU40" t="inlineStr"/>
-      <c r="AV40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr"/>
-      <c r="AX40" t="inlineStr"/>
-      <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="n">
         <v>0</v>
       </c>
@@ -7121,8 +6809,6 @@
           <t>aliphatic</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>2</v>
       </c>
@@ -7237,12 +6923,6 @@
       <c r="AS41" t="n">
         <v>0.0485</v>
       </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AU41" t="inlineStr"/>
-      <c r="AV41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr"/>
-      <c r="AX41" t="inlineStr"/>
-      <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="n">
         <v>82.70543350540082</v>
       </c>
@@ -7285,8 +6965,6 @@
           <t>aliphatic</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
         <v>2</v>
       </c>
@@ -7401,12 +7079,6 @@
       <c r="AS42" t="n">
         <v>0.07099999999999999</v>
       </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AU42" t="inlineStr"/>
-      <c r="AV42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr"/>
-      <c r="AX42" t="inlineStr"/>
-      <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="n">
         <v>79.2215251013251</v>
       </c>
@@ -7449,8 +7121,6 @@
           <t>aliphatic</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>1</v>
       </c>
@@ -7565,12 +7235,6 @@
       <c r="AS43" t="n">
         <v>0.102</v>
       </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AU43" t="inlineStr"/>
-      <c r="AV43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr"/>
-      <c r="AX43" t="inlineStr"/>
-      <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="n">
         <v>98.77941918778983</v>
       </c>
@@ -7613,8 +7277,6 @@
           <t>aliphatic</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>1</v>
       </c>
@@ -7729,12 +7391,6 @@
       <c r="AS44" t="n">
         <v>0.074</v>
       </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AU44" t="inlineStr"/>
-      <c r="AV44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr"/>
-      <c r="AX44" t="inlineStr"/>
-      <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="n">
         <v>93.17650795373589</v>
       </c>
@@ -7777,8 +7433,6 @@
           <t>hetero</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>1</v>
       </c>
@@ -7893,12 +7547,6 @@
       <c r="AS45" t="n">
         <v>0.1716666666666667</v>
       </c>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AU45" t="inlineStr"/>
-      <c r="AV45" t="inlineStr"/>
-      <c r="AW45" t="inlineStr"/>
-      <c r="AX45" t="inlineStr"/>
-      <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="n">
         <v>65.33138833749211</v>
       </c>
@@ -7941,8 +7589,6 @@
           <t>aliphatic</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>2</v>
       </c>
@@ -8057,12 +7703,6 @@
       <c r="AS46" t="n">
         <v>0.0575</v>
       </c>
-      <c r="AT46" t="inlineStr"/>
-      <c r="AU46" t="inlineStr"/>
-      <c r="AV46" t="inlineStr"/>
-      <c r="AW46" t="inlineStr"/>
-      <c r="AX46" t="inlineStr"/>
-      <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="n">
         <v>74.65405947520721</v>
       </c>
@@ -8105,8 +7745,6 @@
           <t>aliphatic</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>2</v>
       </c>
@@ -8221,12 +7859,6 @@
       <c r="AS47" t="n">
         <v>0.1345</v>
       </c>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AU47" t="inlineStr"/>
-      <c r="AV47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr"/>
-      <c r="AX47" t="inlineStr"/>
-      <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="n">
         <v>77.28294082424483</v>
       </c>
@@ -8256,7 +7888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO56"/>
+  <dimension ref="A1:AO51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8490,7 +8122,6 @@
           <t>1_aliphatic</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
         <v>8.752000000000001</v>
       </c>
@@ -8581,10 +8212,6 @@
       <c r="AJ2" t="n">
         <v>0.018</v>
       </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -8615,7 +8242,6 @@
           <t>1_aromatic</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
         <v>8.264200000000001</v>
       </c>
@@ -8706,10 +8332,6 @@
       <c r="AJ3" t="n">
         <v>0.047</v>
       </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -8740,7 +8362,6 @@
           <t>1_aromatic</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
         <v>7.396</v>
       </c>
@@ -8831,10 +8452,6 @@
       <c r="AJ4" t="n">
         <v>0.045</v>
       </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -8865,7 +8482,6 @@
           <t>1_aromatic</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
         <v>8.0669</v>
       </c>
@@ -8956,10 +8572,6 @@
       <c r="AJ5" t="n">
         <v>0.049</v>
       </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -8990,7 +8602,6 @@
           <t>1_aromatic</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
         <v>7.2577</v>
       </c>
@@ -9081,10 +8692,6 @@
       <c r="AJ6" t="n">
         <v>0.045</v>
       </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -9115,7 +8722,6 @@
           <t>1_aromatic</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
         <v>7.3118</v>
       </c>
@@ -9206,10 +8812,6 @@
       <c r="AJ7" t="n">
         <v>0.033</v>
       </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -9240,7 +8842,6 @@
           <t>1_aromatic</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
         <v>7.6513</v>
       </c>
@@ -9331,10 +8932,6 @@
       <c r="AJ8" t="n">
         <v>0.029</v>
       </c>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -9365,7 +8962,6 @@
           <t>2_aliphatic</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
         <v>7.4118</v>
       </c>
@@ -9456,10 +9052,6 @@
       <c r="AJ9" t="n">
         <v>-0.011</v>
       </c>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -9490,7 +9082,6 @@
           <t>1_aromatic</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
         <v>7.3516</v>
       </c>
@@ -9581,10 +9172,6 @@
       <c r="AJ10" t="n">
         <v>0.034</v>
       </c>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -9615,7 +9202,6 @@
           <t>1_aromatic</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
         <v>7.62</v>
       </c>
@@ -9706,10 +9292,6 @@
       <c r="AJ11" t="n">
         <v>0.023</v>
       </c>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -9740,7 +9322,6 @@
           <t>1_aromatic</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
         <v>7.5505</v>
       </c>
@@ -9831,10 +9412,6 @@
       <c r="AJ12" t="n">
         <v>0.034</v>
       </c>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -9865,7 +9442,6 @@
           <t>1_aromatic</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
         <v>7.5148</v>
       </c>
@@ -9956,10 +9532,6 @@
       <c r="AJ13" t="n">
         <v>0.041</v>
       </c>
-      <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -9990,7 +9562,6 @@
           <t>2_aliphatic</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
         <v>8.004300000000001</v>
       </c>
@@ -10081,10 +9652,6 @@
       <c r="AJ14" t="n">
         <v>-0.0135</v>
       </c>
-      <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -10115,7 +9682,6 @@
           <t>1_aromatic</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
         <v>8.044700000000001</v>
       </c>
@@ -10206,10 +9772,6 @@
       <c r="AJ15" t="n">
         <v>0.04</v>
       </c>
-      <c r="AK15" t="inlineStr"/>
-      <c r="AL15" t="inlineStr"/>
-      <c r="AM15" t="inlineStr"/>
-      <c r="AN15" t="inlineStr"/>
       <c r="AO15" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -10240,7 +9802,6 @@
           <t>2_aliphatic</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
         <v>8.0831</v>
       </c>
@@ -10331,10 +9892,6 @@
       <c r="AJ16" t="n">
         <v>-0.029</v>
       </c>
-      <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="inlineStr"/>
-      <c r="AM16" t="inlineStr"/>
-      <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -10365,7 +9922,6 @@
           <t>1_hetero</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
         <v>7.5766</v>
       </c>
@@ -10456,10 +10012,6 @@
       <c r="AJ17" t="n">
         <v>0.035</v>
       </c>
-      <c r="AK17" t="inlineStr"/>
-      <c r="AL17" t="inlineStr"/>
-      <c r="AM17" t="inlineStr"/>
-      <c r="AN17" t="inlineStr"/>
       <c r="AO17" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -10490,7 +10042,6 @@
           <t>1_aromatic</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
         <v>8.0609</v>
       </c>
@@ -10581,10 +10132,6 @@
       <c r="AJ18" t="n">
         <v>0.033</v>
       </c>
-      <c r="AK18" t="inlineStr"/>
-      <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="inlineStr"/>
-      <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -10615,7 +10162,6 @@
           <t>2_aliphatic</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
         <v>8.207000000000001</v>
       </c>
@@ -10706,10 +10252,6 @@
       <c r="AJ19" t="n">
         <v>-0.032</v>
       </c>
-      <c r="AK19" t="inlineStr"/>
-      <c r="AL19" t="inlineStr"/>
-      <c r="AM19" t="inlineStr"/>
-      <c r="AN19" t="inlineStr"/>
       <c r="AO19" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -10740,7 +10282,6 @@
           <t>1_aromatic</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
         <v>8.264099999999999</v>
       </c>
@@ -10831,10 +10372,6 @@
       <c r="AJ20" t="n">
         <v>0.039</v>
       </c>
-      <c r="AK20" t="inlineStr"/>
-      <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="inlineStr"/>
-      <c r="AN20" t="inlineStr"/>
       <c r="AO20" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -10865,7 +10402,6 @@
           <t>1_aromatic</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
         <v>7.3704</v>
       </c>
@@ -10956,10 +10492,6 @@
       <c r="AJ21" t="n">
         <v>0.035</v>
       </c>
-      <c r="AK21" t="inlineStr"/>
-      <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="inlineStr"/>
-      <c r="AN21" t="inlineStr"/>
       <c r="AO21" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -10990,7 +10522,6 @@
           <t>1_aliphatic</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
         <v>8.479699999999999</v>
       </c>
@@ -11081,10 +10612,6 @@
       <c r="AJ22" t="n">
         <v>-0.001</v>
       </c>
-      <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr"/>
-      <c r="AN22" t="inlineStr"/>
       <c r="AO22" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -11115,7 +10642,6 @@
           <t>2_aliphatic</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
         <v>7.8187</v>
       </c>
@@ -11206,10 +10732,6 @@
       <c r="AJ23" t="n">
         <v>-0.005</v>
       </c>
-      <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="inlineStr"/>
-      <c r="AM23" t="inlineStr"/>
-      <c r="AN23" t="inlineStr"/>
       <c r="AO23" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -11240,7 +10762,6 @@
           <t>1_aromatic</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
         <v>7.5235</v>
       </c>
@@ -11331,10 +10852,6 @@
       <c r="AJ24" t="n">
         <v>0.041</v>
       </c>
-      <c r="AK24" t="inlineStr"/>
-      <c r="AL24" t="inlineStr"/>
-      <c r="AM24" t="inlineStr"/>
-      <c r="AN24" t="inlineStr"/>
       <c r="AO24" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -11365,7 +10882,6 @@
           <t>1_aromatic</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
         <v>7.639</v>
       </c>
@@ -11456,10 +10972,6 @@
       <c r="AJ25" t="n">
         <v>0.046</v>
       </c>
-      <c r="AK25" t="inlineStr"/>
-      <c r="AL25" t="inlineStr"/>
-      <c r="AM25" t="inlineStr"/>
-      <c r="AN25" t="inlineStr"/>
       <c r="AO25" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -11490,7 +11002,6 @@
           <t>1_aromatic</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
         <v>7.8349</v>
       </c>
@@ -11581,10 +11092,6 @@
       <c r="AJ26" t="n">
         <v>0.043</v>
       </c>
-      <c r="AK26" t="inlineStr"/>
-      <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="inlineStr"/>
-      <c r="AN26" t="inlineStr"/>
       <c r="AO26" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -11615,7 +11122,6 @@
           <t>2_aliphatic</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
         <v>7.6647</v>
       </c>
@@ -11706,10 +11212,6 @@
       <c r="AJ27" t="n">
         <v>-0.0095</v>
       </c>
-      <c r="AK27" t="inlineStr"/>
-      <c r="AL27" t="inlineStr"/>
-      <c r="AM27" t="inlineStr"/>
-      <c r="AN27" t="inlineStr"/>
       <c r="AO27" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -11740,7 +11242,6 @@
           <t>1_aromatic</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
         <v>7.5401</v>
       </c>
@@ -11831,10 +11332,6 @@
       <c r="AJ28" t="n">
         <v>0.043</v>
       </c>
-      <c r="AK28" t="inlineStr"/>
-      <c r="AL28" t="inlineStr"/>
-      <c r="AM28" t="inlineStr"/>
-      <c r="AN28" t="inlineStr"/>
       <c r="AO28" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -11865,7 +11362,6 @@
           <t>1_mixture</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
         <v>7.4887</v>
       </c>
@@ -11956,10 +11452,6 @@
       <c r="AJ29" t="n">
         <v>0.003</v>
       </c>
-      <c r="AK29" t="inlineStr"/>
-      <c r="AL29" t="inlineStr"/>
-      <c r="AM29" t="inlineStr"/>
-      <c r="AN29" t="inlineStr"/>
       <c r="AO29" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -11990,7 +11482,6 @@
           <t>1_aromatic</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
         <v>7.5854</v>
       </c>
@@ -12081,10 +11572,6 @@
       <c r="AJ30" t="n">
         <v>0.046</v>
       </c>
-      <c r="AK30" t="inlineStr"/>
-      <c r="AL30" t="inlineStr"/>
-      <c r="AM30" t="inlineStr"/>
-      <c r="AN30" t="inlineStr"/>
       <c r="AO30" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -12115,7 +11602,6 @@
           <t>2_aliphatic</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
         <v>7.6496</v>
       </c>
@@ -12206,10 +11692,6 @@
       <c r="AJ31" t="n">
         <v>-0.007</v>
       </c>
-      <c r="AK31" t="inlineStr"/>
-      <c r="AL31" t="inlineStr"/>
-      <c r="AM31" t="inlineStr"/>
-      <c r="AN31" t="inlineStr"/>
       <c r="AO31" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -12240,7 +11722,6 @@
           <t>2_mixture</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
         <v>7.9006</v>
       </c>
@@ -12331,10 +11812,6 @@
       <c r="AJ32" t="n">
         <v>0.0015</v>
       </c>
-      <c r="AK32" t="inlineStr"/>
-      <c r="AL32" t="inlineStr"/>
-      <c r="AM32" t="inlineStr"/>
-      <c r="AN32" t="inlineStr"/>
       <c r="AO32" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -12365,7 +11842,6 @@
           <t>1_aromatic</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
         <v>8.3612</v>
       </c>
@@ -12456,10 +11932,6 @@
       <c r="AJ33" t="n">
         <v>0.048</v>
       </c>
-      <c r="AK33" t="inlineStr"/>
-      <c r="AL33" t="inlineStr"/>
-      <c r="AM33" t="inlineStr"/>
-      <c r="AN33" t="inlineStr"/>
       <c r="AO33" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -12490,7 +11962,6 @@
           <t>2_aliphatic</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
         <v>7.4486</v>
       </c>
@@ -12581,10 +12052,6 @@
       <c r="AJ34" t="n">
         <v>-0.0135</v>
       </c>
-      <c r="AK34" t="inlineStr"/>
-      <c r="AL34" t="inlineStr"/>
-      <c r="AM34" t="inlineStr"/>
-      <c r="AN34" t="inlineStr"/>
       <c r="AO34" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -12615,7 +12082,6 @@
           <t>1_aromatic</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
         <v>7.6952</v>
       </c>
@@ -12706,10 +12172,6 @@
       <c r="AJ35" t="n">
         <v>0.035</v>
       </c>
-      <c r="AK35" t="inlineStr"/>
-      <c r="AL35" t="inlineStr"/>
-      <c r="AM35" t="inlineStr"/>
-      <c r="AN35" t="inlineStr"/>
       <c r="AO35" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -12740,7 +12202,6 @@
           <t>1_aromatic</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
         <v>7.7423</v>
       </c>
@@ -12831,10 +12292,6 @@
       <c r="AJ36" t="n">
         <v>0.025</v>
       </c>
-      <c r="AK36" t="inlineStr"/>
-      <c r="AL36" t="inlineStr"/>
-      <c r="AM36" t="inlineStr"/>
-      <c r="AN36" t="inlineStr"/>
       <c r="AO36" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -12865,7 +12322,6 @@
           <t>1_aromatic</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
         <v>7.4155</v>
       </c>
@@ -12956,10 +12412,6 @@
       <c r="AJ37" t="n">
         <v>0.032</v>
       </c>
-      <c r="AK37" t="inlineStr"/>
-      <c r="AL37" t="inlineStr"/>
-      <c r="AM37" t="inlineStr"/>
-      <c r="AN37" t="inlineStr"/>
       <c r="AO37" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -12990,7 +12442,6 @@
           <t>2_aliphatic</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
         <v>6.9447</v>
       </c>
@@ -13081,10 +12532,6 @@
       <c r="AJ38" t="n">
         <v>-0.016</v>
       </c>
-      <c r="AK38" t="inlineStr"/>
-      <c r="AL38" t="inlineStr"/>
-      <c r="AM38" t="inlineStr"/>
-      <c r="AN38" t="inlineStr"/>
       <c r="AO38" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -13115,7 +12562,6 @@
           <t>1_aromatic</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
         <v>6.5733</v>
       </c>
@@ -13206,10 +12652,6 @@
       <c r="AJ39" t="n">
         <v>0.039</v>
       </c>
-      <c r="AK39" t="inlineStr"/>
-      <c r="AL39" t="inlineStr"/>
-      <c r="AM39" t="inlineStr"/>
-      <c r="AN39" t="inlineStr"/>
       <c r="AO39" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -13240,7 +12682,6 @@
           <t>1_aromatic</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
         <v>7.5233</v>
       </c>
@@ -13331,10 +12772,6 @@
       <c r="AJ40" t="n">
         <v>0.03</v>
       </c>
-      <c r="AK40" t="inlineStr"/>
-      <c r="AL40" t="inlineStr"/>
-      <c r="AM40" t="inlineStr"/>
-      <c r="AN40" t="inlineStr"/>
       <c r="AO40" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -13365,7 +12802,6 @@
           <t>1_aromatic</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
         <v>7.4337</v>
       </c>
@@ -13456,10 +12892,6 @@
       <c r="AJ41" t="n">
         <v>0.029</v>
       </c>
-      <c r="AK41" t="inlineStr"/>
-      <c r="AL41" t="inlineStr"/>
-      <c r="AM41" t="inlineStr"/>
-      <c r="AN41" t="inlineStr"/>
       <c r="AO41" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -13490,7 +12922,6 @@
           <t>1_aromatic</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
         <v>7.883</v>
       </c>
@@ -13581,10 +13012,6 @@
       <c r="AJ42" t="n">
         <v>0.037</v>
       </c>
-      <c r="AK42" t="inlineStr"/>
-      <c r="AL42" t="inlineStr"/>
-      <c r="AM42" t="inlineStr"/>
-      <c r="AN42" t="inlineStr"/>
       <c r="AO42" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -13615,7 +13042,6 @@
           <t>1_aromatic</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
         <v>7.3843</v>
       </c>
@@ -13706,10 +13132,6 @@
       <c r="AJ43" t="n">
         <v>0.039</v>
       </c>
-      <c r="AK43" t="inlineStr"/>
-      <c r="AL43" t="inlineStr"/>
-      <c r="AM43" t="inlineStr"/>
-      <c r="AN43" t="inlineStr"/>
       <c r="AO43" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -13740,7 +13162,6 @@
           <t>1_aromatic</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
         <v>7.4141</v>
       </c>
@@ -13831,10 +13252,6 @@
       <c r="AJ44" t="n">
         <v>0.04</v>
       </c>
-      <c r="AK44" t="inlineStr"/>
-      <c r="AL44" t="inlineStr"/>
-      <c r="AM44" t="inlineStr"/>
-      <c r="AN44" t="inlineStr"/>
       <c r="AO44" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -13865,7 +13282,6 @@
           <t>1_aromatic</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
         <v>7.1858</v>
       </c>
@@ -13956,10 +13372,6 @@
       <c r="AJ45" t="n">
         <v>0.034</v>
       </c>
-      <c r="AK45" t="inlineStr"/>
-      <c r="AL45" t="inlineStr"/>
-      <c r="AM45" t="inlineStr"/>
-      <c r="AN45" t="inlineStr"/>
       <c r="AO45" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -13990,7 +13402,6 @@
           <t>1_aromatic</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
         <v>7.0937</v>
       </c>
@@ -14081,10 +13492,6 @@
       <c r="AJ46" t="n">
         <v>0.036</v>
       </c>
-      <c r="AK46" t="inlineStr"/>
-      <c r="AL46" t="inlineStr"/>
-      <c r="AM46" t="inlineStr"/>
-      <c r="AN46" t="inlineStr"/>
       <c r="AO46" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -14115,7 +13522,6 @@
           <t>1_aromatic</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
         <v>7.2416</v>
       </c>
@@ -14206,10 +13612,6 @@
       <c r="AJ47" t="n">
         <v>0.033</v>
       </c>
-      <c r="AK47" t="inlineStr"/>
-      <c r="AL47" t="inlineStr"/>
-      <c r="AM47" t="inlineStr"/>
-      <c r="AN47" t="inlineStr"/>
       <c r="AO47" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -14240,7 +13642,6 @@
           <t>1_aromatic</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
         <v>7.2985</v>
       </c>
@@ -14331,10 +13732,6 @@
       <c r="AJ48" t="n">
         <v>0.026</v>
       </c>
-      <c r="AK48" t="inlineStr"/>
-      <c r="AL48" t="inlineStr"/>
-      <c r="AM48" t="inlineStr"/>
-      <c r="AN48" t="inlineStr"/>
       <c r="AO48" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -14343,21 +13740,21 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>49_amine_pka.sdf</t>
+          <t>54_amine.sdf</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CCNCC</t>
+          <t>CNCCC(OC1=CC=C(C(F)(F)F)C=C1)C2=CC=CC=C2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>train</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -14365,101 +13762,96 @@
           <t>2_aliphatic</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
-        <v>8.285299999999999</v>
+        <v>7.7229</v>
       </c>
       <c r="H49" t="n">
-        <v>-4.1825</v>
+        <v>4.6077</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3480601</v>
+        <v>-0.3704896</v>
       </c>
       <c r="J49" t="n">
-        <v>0.0368907</v>
+        <v>-0.2530449</v>
       </c>
       <c r="K49" t="n">
-        <v>0.003982511205258396</v>
+        <v>0.8797392504742045</v>
       </c>
       <c r="L49" t="n">
-        <v>-8.285299999999999</v>
+        <v>-7.7229</v>
       </c>
       <c r="M49" t="n">
-        <v>12.4678</v>
+        <v>3.1152</v>
       </c>
       <c r="N49" t="n">
-        <v>79.43332079385748</v>
+        <v>84.74442462931124</v>
       </c>
       <c r="O49" t="n">
-        <v>249.7903851069101</v>
+        <v>543.7803728288163</v>
       </c>
       <c r="P49" t="n">
-        <v>334.5201004812312</v>
+        <v>863.3668860503931</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.7221007849307814</v>
+        <v>0.7707329513503187</v>
       </c>
       <c r="R49" t="n">
-        <v>13.85298214088126</v>
+        <v>18.56581163521069</v>
       </c>
       <c r="S49" t="n">
-        <v>17.91449714602106</v>
+        <v>25.01488283507465</v>
       </c>
       <c r="T49" t="n">
-        <v>-0.26311906</v>
+        <v>-0.26273297</v>
       </c>
       <c r="U49" t="n">
-        <v>0.201</v>
+        <v>-0.006</v>
       </c>
       <c r="V49" t="n">
-        <v>0.209</v>
+        <v>0.106</v>
       </c>
       <c r="W49" t="n">
-        <v>71.86933833265194</v>
+        <v>41.63014296230146</v>
       </c>
       <c r="X49" t="n">
-        <v>4.663249061401421</v>
+        <v>3.558774266117303</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.833290047101321</v>
+        <v>2.389583602796272</v>
       </c>
       <c r="Z49" t="n">
-        <v>4.394190095053111</v>
+        <v>8.040122281186608</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.01400362</v>
+        <v>-0.02639989</v>
       </c>
       <c r="AB49" t="n">
-        <v>-0.004</v>
+        <v>-0.007</v>
       </c>
       <c r="AC49" t="n">
-        <v>-0.028</v>
+        <v>-0.033</v>
       </c>
       <c r="AD49" t="n">
-        <v>71.73337072756942</v>
+        <v>64.73836039840145</v>
       </c>
       <c r="AE49" t="n">
-        <v>4.660042080097437</v>
+        <v>5.322956258478133</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.913309433880936</v>
+        <v>2.298877572526639</v>
       </c>
       <c r="AG49" t="n">
-        <v>4.391390758795119</v>
+        <v>9.194387128400255</v>
       </c>
       <c r="AH49" t="n">
-        <v>0.018223995</v>
+        <v>-0.006035959999999999</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.001</v>
+        <v>-0.006500000000000001</v>
       </c>
       <c r="AJ49" t="n">
-        <v>-0.032</v>
-      </c>
-      <c r="AK49" t="inlineStr"/>
-      <c r="AL49" t="inlineStr"/>
-      <c r="AM49" t="inlineStr"/>
-      <c r="AN49" t="inlineStr"/>
+        <v>-0.029</v>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -14468,21 +13860,21 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>50_amine_pka.sdf</t>
+          <t>55_amine.sdf</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CCCCC(CC)CNCC(CC)CCCC</t>
+          <t>FC(C=C1)=CC=C1[C@H]2[C@H](COC3=CC4=C(OCO4)C=C3)CNCC2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>train</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -14490,101 +13882,96 @@
           <t>2_aliphatic</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
-        <v>7.2648</v>
+        <v>7.0442</v>
       </c>
       <c r="H50" t="n">
-        <v>-2.9376</v>
+        <v>4.462700000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3365342</v>
+        <v>-0.3483849</v>
       </c>
       <c r="J50" t="n">
-        <v>0.0226859</v>
+        <v>-0.240738</v>
       </c>
       <c r="K50" t="n">
-        <v>0.00223149816585703</v>
+        <v>0.746840076073785</v>
       </c>
       <c r="L50" t="n">
-        <v>-7.2648</v>
+        <v>-7.0442</v>
       </c>
       <c r="M50" t="n">
-        <v>10.2024</v>
+        <v>2.581499999999999</v>
       </c>
       <c r="N50" t="n">
-        <v>103.930499611108</v>
+        <v>77.91675904486023</v>
       </c>
       <c r="O50" t="n">
-        <v>551.6510242598189</v>
+        <v>548.4392242446406</v>
       </c>
       <c r="P50" t="n">
-        <v>885.7783908030739</v>
+        <v>892.5407731551846</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.7060435735793235</v>
+        <v>0.6990890463802076</v>
       </c>
       <c r="R50" t="n">
-        <v>17.04681819965307</v>
+        <v>19.29683579511405</v>
       </c>
       <c r="S50" t="n">
-        <v>26.11301408517225</v>
+        <v>19.46718568722174</v>
       </c>
       <c r="T50" t="n">
-        <v>-0.26802536</v>
+        <v>-0.26078449</v>
       </c>
       <c r="U50" t="n">
-        <v>0.077</v>
+        <v>0.007</v>
       </c>
       <c r="V50" t="n">
-        <v>0.137</v>
+        <v>0.113</v>
       </c>
       <c r="W50" t="n">
-        <v>102.8532178169928</v>
+        <v>89.07865351747991</v>
       </c>
       <c r="X50" t="n">
-        <v>6.96246603284858</v>
+        <v>11.71338979856453</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.447828035225065</v>
+        <v>2.120749012350302</v>
       </c>
       <c r="Z50" t="n">
-        <v>7.676025611022537</v>
+        <v>9.23312950453003</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.01373423</v>
+        <v>0.01063574</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.006</v>
+        <v>-0.006</v>
       </c>
       <c r="AC50" t="n">
-        <v>-0.029</v>
+        <v>-0.019</v>
       </c>
       <c r="AD50" t="n">
-        <v>101.8768658220349</v>
+        <v>84.34227428966335</v>
       </c>
       <c r="AE50" t="n">
-        <v>6.91964884093241</v>
+        <v>9.66173593511337</v>
       </c>
       <c r="AF50" t="n">
-        <v>2.940845948718732</v>
+        <v>2.005940621475329</v>
       </c>
       <c r="AG50" t="n">
-        <v>6.753268008876645</v>
+        <v>9.859112824782123</v>
       </c>
       <c r="AH50" t="n">
-        <v>0.011376885</v>
+        <v>0.01577884</v>
       </c>
       <c r="AI50" t="n">
-        <v>0.003</v>
+        <v>-0.006500000000000001</v>
       </c>
       <c r="AJ50" t="n">
-        <v>-0.0255</v>
-      </c>
-      <c r="AK50" t="inlineStr"/>
-      <c r="AL50" t="inlineStr"/>
-      <c r="AM50" t="inlineStr"/>
-      <c r="AN50" t="inlineStr"/>
+        <v>-0.0215</v>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
@@ -14593,21 +13980,21 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>51_amine_pka.sdf</t>
+          <t>56_amine.sdf</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>C1CCNC1</t>
+          <t>C[C@@H](NCCCC1=CC(C(F)(F)F)=CC=C1)C2=CC=CC3=CC=CC=C32</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>train</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -14615,727 +14002,97 @@
           <t>2_aliphatic</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
-        <v>8.7279</v>
+        <v>7.2288</v>
       </c>
       <c r="H51" t="n">
-        <v>-4.0925</v>
+        <v>5.457400000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3588752</v>
+        <v>-0.3542657</v>
       </c>
       <c r="J51" t="n">
-        <v>0.0348158</v>
+        <v>-0.2667249</v>
       </c>
       <c r="K51" t="n">
-        <v>0.0003123390967909946</v>
+        <v>1.161355326701325</v>
       </c>
       <c r="L51" t="n">
-        <v>-8.7279</v>
+        <v>-7.2288</v>
       </c>
       <c r="M51" t="n">
-        <v>12.8204</v>
+        <v>1.771399999999999</v>
       </c>
       <c r="N51" t="n">
-        <v>71.80449224407411</v>
+        <v>109.1464261230041</v>
       </c>
       <c r="O51" t="n">
-        <v>228.2701386081276</v>
+        <v>613.9811635658186</v>
       </c>
       <c r="P51" t="n">
-        <v>299.5718464349987</v>
+        <v>997.5143014788903</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.8330043541206633</v>
+        <v>0.7131521585529299</v>
       </c>
       <c r="R51" t="n">
-        <v>13.80790517738682</v>
+        <v>19.40831026130166</v>
       </c>
       <c r="S51" t="n">
-        <v>15.86116670278684</v>
+        <v>25.83426273868252</v>
       </c>
       <c r="T51" t="n">
-        <v>-0.26304157</v>
+        <v>-0.26504251</v>
       </c>
       <c r="U51" t="n">
-        <v>0.164</v>
+        <v>0.005</v>
       </c>
       <c r="V51" t="n">
-        <v>0.213</v>
+        <v>0.098</v>
       </c>
       <c r="W51" t="n">
-        <v>67.25166928311896</v>
+        <v>119.4569542068763</v>
       </c>
       <c r="X51" t="n">
-        <v>4.260720092580045</v>
+        <v>5.729818543901297</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.7</v>
+        <v>3.116506411828478</v>
       </c>
       <c r="Z51" t="n">
-        <v>4.234765885876793</v>
+        <v>10.13442931288407</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.01240695</v>
+        <v>0.05226507</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.008</v>
+        <v>-0.003</v>
       </c>
       <c r="AC51" t="n">
-        <v>-0.034</v>
+        <v>-0.013</v>
       </c>
       <c r="AD51" t="n">
-        <v>67.23127414235658</v>
+        <v>101.3089395946518</v>
       </c>
       <c r="AE51" t="n">
-        <v>4.26073080042301</v>
+        <v>7.096208590750437</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.7</v>
+        <v>3.038307766586796</v>
       </c>
       <c r="AG51" t="n">
-        <v>4.234753845431678</v>
+        <v>9.168385090730283</v>
       </c>
       <c r="AH51" t="n">
-        <v>0.012407485</v>
+        <v>0.031659935</v>
       </c>
       <c r="AI51" t="n">
-        <v>0.008</v>
+        <v>-0.005</v>
       </c>
       <c r="AJ51" t="n">
-        <v>-0.034</v>
-      </c>
-      <c r="AK51" t="inlineStr"/>
-      <c r="AL51" t="inlineStr"/>
-      <c r="AM51" t="inlineStr"/>
-      <c r="AN51" t="inlineStr"/>
+        <v>-0.0155</v>
+      </c>
       <c r="AO51" t="inlineStr">
-        <is>
-          <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>52</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>52_amine_pka.sdf</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>C1CN(CCN1)C2=CC=CC=C2F</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>train</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>2_aliphatic</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="n">
-        <v>7.2595</v>
-      </c>
-      <c r="H52" t="n">
-        <v>3.1841</v>
-      </c>
-      <c r="I52" t="n">
-        <v>-0.3514081</v>
-      </c>
-      <c r="J52" t="n">
-        <v>-0.2285967</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0.4391194219473373</v>
-      </c>
-      <c r="L52" t="n">
-        <v>-7.2595</v>
-      </c>
-      <c r="M52" t="n">
-        <v>4.0754</v>
-      </c>
-      <c r="N52" t="n">
-        <v>75.93581562927349</v>
-      </c>
-      <c r="O52" t="n">
-        <v>360.6608585893403</v>
-      </c>
-      <c r="P52" t="n">
-        <v>542.3565843771303</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>0.8357005038794446</v>
-      </c>
-      <c r="R52" t="n">
-        <v>17.34142790848705</v>
-      </c>
-      <c r="S52" t="n">
-        <v>16.88142584293871</v>
-      </c>
-      <c r="T52" t="n">
-        <v>-0.25716689</v>
-      </c>
-      <c r="U52" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="V52" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="W52" t="n">
-        <v>74.44853921060172</v>
-      </c>
-      <c r="X52" t="n">
-        <v>5.736026245535466</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>8.713026840281024</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>0.00462222</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>-0.008</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>74.04063639535418</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>5.857972623134188</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>8.545387093089111</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>0.00466215</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>-0.008500000000000001</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>-0.0185</v>
-      </c>
-      <c r="AK52" t="inlineStr"/>
-      <c r="AL52" t="inlineStr"/>
-      <c r="AM52" t="inlineStr"/>
-      <c r="AN52" t="inlineStr"/>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>53</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>53_amine_pka.sdf</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>CNCC1=C2C=CC=CC2=CC3=CC=CC=C31</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>train</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>2_aliphatic</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="n">
-        <v>6.8633</v>
-      </c>
-      <c r="H53" t="n">
-        <v>5.4797</v>
-      </c>
-      <c r="I53" t="n">
-        <v>-0.3524368</v>
-      </c>
-      <c r="J53" t="n">
-        <v>-0.2844458</v>
-      </c>
-      <c r="K53" t="n">
-        <v>1.128022231341606</v>
-      </c>
-      <c r="L53" t="n">
-        <v>-6.8633</v>
-      </c>
-      <c r="M53" t="n">
-        <v>1.383599999999999</v>
-      </c>
-      <c r="N53" t="n">
-        <v>84.73187377345748</v>
-      </c>
-      <c r="O53" t="n">
-        <v>431.5234153336622</v>
-      </c>
-      <c r="P53" t="n">
-        <v>673.96679174717</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0.7535009409900633</v>
-      </c>
-      <c r="R53" t="n">
-        <v>19.14322972107084</v>
-      </c>
-      <c r="S53" t="n">
-        <v>23.17893961110984</v>
-      </c>
-      <c r="T53" t="n">
-        <v>-0.25352024</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="V53" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="W53" t="n">
-        <v>41.49417535721895</v>
-      </c>
-      <c r="X53" t="n">
-        <v>3.554144906470567</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>2.00699287602134</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>6.333340735680872</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>-0.02199688</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>-0.013</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>-0.028</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>68.98316443861201</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>4.47164532280181</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>2.509727900078337</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>6.793688375622419</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>-0.00325727</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>-0.012</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>-0.025</v>
-      </c>
-      <c r="AK53" t="inlineStr"/>
-      <c r="AL53" t="inlineStr"/>
-      <c r="AM53" t="inlineStr"/>
-      <c r="AN53" t="inlineStr"/>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>54</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>54_amine.sdf</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>CNCCC(OC1=CC=C(C(F)(F)F)C=C1)C2=CC=CC=C2</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>2_aliphatic</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="n">
-        <v>7.7229</v>
-      </c>
-      <c r="H54" t="n">
-        <v>4.6077</v>
-      </c>
-      <c r="I54" t="n">
-        <v>-0.3704896</v>
-      </c>
-      <c r="J54" t="n">
-        <v>-0.2530449</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0.8797392504742045</v>
-      </c>
-      <c r="L54" t="n">
-        <v>-7.7229</v>
-      </c>
-      <c r="M54" t="n">
-        <v>3.1152</v>
-      </c>
-      <c r="N54" t="n">
-        <v>84.74442462931124</v>
-      </c>
-      <c r="O54" t="n">
-        <v>543.7803728288163</v>
-      </c>
-      <c r="P54" t="n">
-        <v>863.3668860503931</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0.7707329513503187</v>
-      </c>
-      <c r="R54" t="n">
-        <v>18.56581163521069</v>
-      </c>
-      <c r="S54" t="n">
-        <v>25.01488283507465</v>
-      </c>
-      <c r="T54" t="n">
-        <v>-0.26273297</v>
-      </c>
-      <c r="U54" t="n">
-        <v>-0.006</v>
-      </c>
-      <c r="V54" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="W54" t="n">
-        <v>41.63014296230146</v>
-      </c>
-      <c r="X54" t="n">
-        <v>3.558774266117303</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>2.389583602796272</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>8.040122281186608</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>-0.02639989</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>-0.007</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>-0.033</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>64.73836039840145</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>5.322956258478133</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>2.298877572526639</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>9.194387128400255</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>-0.006035959999999999</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>-0.006500000000000001</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>-0.029</v>
-      </c>
-      <c r="AK54" t="inlineStr"/>
-      <c r="AL54" t="inlineStr"/>
-      <c r="AM54" t="inlineStr"/>
-      <c r="AN54" t="inlineStr"/>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>55</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>55_amine.sdf</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>FC(C=C1)=CC=C1[C@H]2[C@H](COC3=CC4=C(OCO4)C=C3)CNCC2</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>2_aliphatic</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="n">
-        <v>7.0442</v>
-      </c>
-      <c r="H55" t="n">
-        <v>4.462700000000001</v>
-      </c>
-      <c r="I55" t="n">
-        <v>-0.3483849</v>
-      </c>
-      <c r="J55" t="n">
-        <v>-0.240738</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0.746840076073785</v>
-      </c>
-      <c r="L55" t="n">
-        <v>-7.0442</v>
-      </c>
-      <c r="M55" t="n">
-        <v>2.581499999999999</v>
-      </c>
-      <c r="N55" t="n">
-        <v>77.91675904486023</v>
-      </c>
-      <c r="O55" t="n">
-        <v>548.4392242446406</v>
-      </c>
-      <c r="P55" t="n">
-        <v>892.5407731551846</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0.6990890463802076</v>
-      </c>
-      <c r="R55" t="n">
-        <v>19.29683579511405</v>
-      </c>
-      <c r="S55" t="n">
-        <v>19.46718568722174</v>
-      </c>
-      <c r="T55" t="n">
-        <v>-0.26078449</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="V55" t="n">
-        <v>0.113</v>
-      </c>
-      <c r="W55" t="n">
-        <v>89.07865351747991</v>
-      </c>
-      <c r="X55" t="n">
-        <v>11.71338979856453</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>2.120749012350302</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>9.23312950453003</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>0.01063574</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>-0.006</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>-0.019</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>84.34227428966335</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>9.66173593511337</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>2.005940621475329</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>9.859112824782123</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>0.01577884</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>-0.006500000000000001</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>-0.0215</v>
-      </c>
-      <c r="AK55" t="inlineStr"/>
-      <c r="AL55" t="inlineStr"/>
-      <c r="AM55" t="inlineStr"/>
-      <c r="AN55" t="inlineStr"/>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>56</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>56_amine.sdf</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>C[C@@H](NCCCC1=CC(C(F)(F)F)=CC=C1)C2=CC=CC3=CC=CC=C32</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>2_aliphatic</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="n">
-        <v>7.2288</v>
-      </c>
-      <c r="H56" t="n">
-        <v>5.457400000000001</v>
-      </c>
-      <c r="I56" t="n">
-        <v>-0.3542657</v>
-      </c>
-      <c r="J56" t="n">
-        <v>-0.2667249</v>
-      </c>
-      <c r="K56" t="n">
-        <v>1.161355326701325</v>
-      </c>
-      <c r="L56" t="n">
-        <v>-7.2288</v>
-      </c>
-      <c r="M56" t="n">
-        <v>1.771399999999999</v>
-      </c>
-      <c r="N56" t="n">
-        <v>109.1464261230041</v>
-      </c>
-      <c r="O56" t="n">
-        <v>613.9811635658186</v>
-      </c>
-      <c r="P56" t="n">
-        <v>997.5143014788903</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0.7131521585529299</v>
-      </c>
-      <c r="R56" t="n">
-        <v>19.40831026130166</v>
-      </c>
-      <c r="S56" t="n">
-        <v>25.83426273868252</v>
-      </c>
-      <c r="T56" t="n">
-        <v>-0.26504251</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="V56" t="n">
-        <v>0.098</v>
-      </c>
-      <c r="W56" t="n">
-        <v>119.4569542068763</v>
-      </c>
-      <c r="X56" t="n">
-        <v>5.729818543901297</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>3.116506411828478</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>10.13442931288407</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>0.05226507</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>-0.003</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>-0.013</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>101.3089395946518</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>7.096208590750437</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>3.038307766586796</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>9.168385090730283</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>0.031659935</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>-0.0155</v>
-      </c>
-      <c r="AK56" t="inlineStr"/>
-      <c r="AL56" t="inlineStr"/>
-      <c r="AM56" t="inlineStr"/>
-      <c r="AN56" t="inlineStr"/>
-      <c r="AO56" t="inlineStr">
         <is>
           <t>rdkit-mmff + morfeus + xtb (prism_ml.descriptors)</t>
         </is>
@@ -15781,16 +14538,6 @@
       <c r="AS2" t="n">
         <v>0.1255</v>
       </c>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
       <c r="BD2" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -15941,16 +14688,6 @@
       <c r="AS3" t="n">
         <v>0.1395</v>
       </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -16101,16 +14838,6 @@
       <c r="AS4" t="n">
         <v>0.1155</v>
       </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -16355,7 +15082,6 @@
       <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>N</t>
@@ -16366,7 +15092,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>8.118600000000001</v>
       </c>
@@ -16457,10 +15182,6 @@
       <c r="AK2" t="n">
         <v>-0.014</v>
       </c>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -16479,7 +15200,6 @@
       <c r="C3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>N</t>
@@ -16490,7 +15210,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>8.258699999999999</v>
       </c>
@@ -16581,10 +15300,6 @@
       <c r="AK3" t="n">
         <v>0.021</v>
       </c>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -16603,7 +15318,6 @@
       <c r="C4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>N</t>
@@ -16614,7 +15328,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>8.417999999999999</v>
       </c>
@@ -16705,10 +15418,6 @@
       <c r="AK4" t="n">
         <v>-0.024</v>
       </c>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -16727,7 +15436,6 @@
       <c r="C5" t="n">
         <v>1</v>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>N</t>
@@ -16738,7 +15446,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>8.215299999999999</v>
       </c>
@@ -16829,10 +15536,6 @@
       <c r="AK5" t="n">
         <v>0.041</v>
       </c>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -16851,7 +15554,6 @@
       <c r="C6" t="n">
         <v>7</v>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>N</t>
@@ -16862,7 +15564,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>8.029999999999999</v>
       </c>
@@ -16953,10 +15654,6 @@
       <c r="AK6" t="n">
         <v>-0.018</v>
       </c>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -16975,7 +15672,6 @@
       <c r="C7" t="n">
         <v>1</v>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>N</t>
@@ -16986,7 +15682,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>8.134499999999999</v>
       </c>
@@ -17077,10 +15772,6 @@
       <c r="AK7" t="n">
         <v>-0.018</v>
       </c>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -17207,10 +15898,6 @@
       <c r="AK8" t="n">
         <v>-0.029</v>
       </c>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -17337,10 +16024,6 @@
       <c r="AK9" t="n">
         <v>-0.0365</v>
       </c>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -17467,10 +16150,6 @@
       <c r="AK10" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -17597,10 +16276,6 @@
       <c r="AK11" t="n">
         <v>0.0605</v>
       </c>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -17727,10 +16402,6 @@
       <c r="AK12" t="n">
         <v>-0.04</v>
       </c>
-      <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -17857,10 +16528,6 @@
       <c r="AK13" t="n">
         <v>-0.0405</v>
       </c>
-      <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="inlineStr"/>
       <c r="AP13" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -17987,10 +16654,6 @@
       <c r="AK14" t="n">
         <v>-0.038</v>
       </c>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="inlineStr"/>
       <c r="AP14" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -18117,10 +16780,6 @@
       <c r="AK15" t="n">
         <v>-0.026</v>
       </c>
-      <c r="AL15" t="inlineStr"/>
-      <c r="AM15" t="inlineStr"/>
-      <c r="AN15" t="inlineStr"/>
-      <c r="AO15" t="inlineStr"/>
       <c r="AP15" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -18247,10 +16906,6 @@
       <c r="AK16" t="n">
         <v>-0.026</v>
       </c>
-      <c r="AL16" t="inlineStr"/>
-      <c r="AM16" t="inlineStr"/>
-      <c r="AN16" t="inlineStr"/>
-      <c r="AO16" t="inlineStr"/>
       <c r="AP16" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -18377,10 +17032,6 @@
       <c r="AK17" t="n">
         <v>-0.0305</v>
       </c>
-      <c r="AL17" t="inlineStr"/>
-      <c r="AM17" t="inlineStr"/>
-      <c r="AN17" t="inlineStr"/>
-      <c r="AO17" t="inlineStr"/>
       <c r="AP17" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -18507,10 +17158,6 @@
       <c r="AK18" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="inlineStr"/>
-      <c r="AN18" t="inlineStr"/>
-      <c r="AO18" t="inlineStr"/>
       <c r="AP18" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -18637,10 +17284,6 @@
       <c r="AK19" t="n">
         <v>-0.024</v>
       </c>
-      <c r="AL19" t="inlineStr"/>
-      <c r="AM19" t="inlineStr"/>
-      <c r="AN19" t="inlineStr"/>
-      <c r="AO19" t="inlineStr"/>
       <c r="AP19" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -18767,10 +17410,6 @@
       <c r="AK20" t="n">
         <v>0.018</v>
       </c>
-      <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="inlineStr"/>
-      <c r="AN20" t="inlineStr"/>
-      <c r="AO20" t="inlineStr"/>
       <c r="AP20" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -18789,7 +17428,6 @@
       <c r="C21" t="n">
         <v>8</v>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>N</t>
@@ -18800,7 +17438,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>8.022600000000001</v>
       </c>
@@ -18891,10 +17528,6 @@
       <c r="AK21" t="n">
         <v>0.032</v>
       </c>
-      <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="inlineStr"/>
-      <c r="AN21" t="inlineStr"/>
-      <c r="AO21" t="inlineStr"/>
       <c r="AP21" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -18913,7 +17546,6 @@
       <c r="C22" t="n">
         <v>9</v>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>N</t>
@@ -18924,7 +17556,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>7.6005</v>
       </c>
@@ -19015,10 +17646,6 @@
       <c r="AK22" t="n">
         <v>0.042</v>
       </c>
-      <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr"/>
-      <c r="AN22" t="inlineStr"/>
-      <c r="AO22" t="inlineStr"/>
       <c r="AP22" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -19037,7 +17664,6 @@
       <c r="C23" t="n">
         <v>1</v>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>N</t>
@@ -19048,7 +17674,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>7.6883</v>
       </c>
@@ -19139,10 +17764,6 @@
       <c r="AK23" t="n">
         <v>0.023</v>
       </c>
-      <c r="AL23" t="inlineStr"/>
-      <c r="AM23" t="inlineStr"/>
-      <c r="AN23" t="inlineStr"/>
-      <c r="AO23" t="inlineStr"/>
       <c r="AP23" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -19161,7 +17782,6 @@
       <c r="C24" t="n">
         <v>6</v>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>N</t>
@@ -19172,7 +17792,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>8.0123</v>
       </c>
@@ -19263,10 +17882,6 @@
       <c r="AK24" t="n">
         <v>0.031</v>
       </c>
-      <c r="AL24" t="inlineStr"/>
-      <c r="AM24" t="inlineStr"/>
-      <c r="AN24" t="inlineStr"/>
-      <c r="AO24" t="inlineStr"/>
       <c r="AP24" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -19393,10 +18008,6 @@
       <c r="AK25" t="n">
         <v>0.015</v>
       </c>
-      <c r="AL25" t="inlineStr"/>
-      <c r="AM25" t="inlineStr"/>
-      <c r="AN25" t="inlineStr"/>
-      <c r="AO25" t="inlineStr"/>
       <c r="AP25" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -19523,10 +18134,6 @@
       <c r="AK26" t="n">
         <v>0.0289999999999999</v>
       </c>
-      <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="inlineStr"/>
-      <c r="AN26" t="inlineStr"/>
-      <c r="AO26" t="inlineStr"/>
       <c r="AP26" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -19545,7 +18152,6 @@
       <c r="C27" t="n">
         <v>1</v>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>N</t>
@@ -19556,7 +18162,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>8.3254</v>
       </c>
@@ -19647,10 +18252,6 @@
       <c r="AK27" t="n">
         <v>0.029</v>
       </c>
-      <c r="AL27" t="inlineStr"/>
-      <c r="AM27" t="inlineStr"/>
-      <c r="AN27" t="inlineStr"/>
-      <c r="AO27" t="inlineStr"/>
       <c r="AP27" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -19669,7 +18270,6 @@
       <c r="C28" t="n">
         <v>1</v>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>N</t>
@@ -19680,7 +18280,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>8.019500000000001</v>
       </c>
@@ -19771,10 +18370,6 @@
       <c r="AK28" t="n">
         <v>-0.006</v>
       </c>
-      <c r="AL28" t="inlineStr"/>
-      <c r="AM28" t="inlineStr"/>
-      <c r="AN28" t="inlineStr"/>
-      <c r="AO28" t="inlineStr"/>
       <c r="AP28" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -19793,7 +18388,6 @@
       <c r="C29" t="n">
         <v>1</v>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>N</t>
@@ -19804,7 +18398,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>7.9228</v>
       </c>
@@ -19895,10 +18488,6 @@
       <c r="AK29" t="n">
         <v>0.001</v>
       </c>
-      <c r="AL29" t="inlineStr"/>
-      <c r="AM29" t="inlineStr"/>
-      <c r="AN29" t="inlineStr"/>
-      <c r="AO29" t="inlineStr"/>
       <c r="AP29" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -20025,10 +18614,6 @@
       <c r="AK30" t="n">
         <v>0.0435</v>
       </c>
-      <c r="AL30" t="inlineStr"/>
-      <c r="AM30" t="inlineStr"/>
-      <c r="AN30" t="inlineStr"/>
-      <c r="AO30" t="inlineStr"/>
       <c r="AP30" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -20155,10 +18740,6 @@
       <c r="AK31" t="n">
         <v>0.0199999999999999</v>
       </c>
-      <c r="AL31" t="inlineStr"/>
-      <c r="AM31" t="inlineStr"/>
-      <c r="AN31" t="inlineStr"/>
-      <c r="AO31" t="inlineStr"/>
       <c r="AP31" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -20177,7 +18758,6 @@
       <c r="C32" t="n">
         <v>1</v>
       </c>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>N</t>
@@ -20188,7 +18768,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>7.2178</v>
       </c>
@@ -20279,10 +18858,6 @@
       <c r="AK32" t="n">
         <v>0.04</v>
       </c>
-      <c r="AL32" t="inlineStr"/>
-      <c r="AM32" t="inlineStr"/>
-      <c r="AN32" t="inlineStr"/>
-      <c r="AO32" t="inlineStr"/>
       <c r="AP32" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -20301,7 +18876,6 @@
       <c r="C33" t="n">
         <v>1</v>
       </c>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>N</t>
@@ -20312,7 +18886,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>7.6181</v>
       </c>
@@ -20403,10 +18976,6 @@
       <c r="AK33" t="n">
         <v>0.042</v>
       </c>
-      <c r="AL33" t="inlineStr"/>
-      <c r="AM33" t="inlineStr"/>
-      <c r="AN33" t="inlineStr"/>
-      <c r="AO33" t="inlineStr"/>
       <c r="AP33" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -20425,7 +18994,6 @@
       <c r="C34" t="n">
         <v>8</v>
       </c>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>N</t>
@@ -20436,7 +19004,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>7.9572</v>
       </c>
@@ -20527,10 +19094,6 @@
       <c r="AK34" t="n">
         <v>0.032</v>
       </c>
-      <c r="AL34" t="inlineStr"/>
-      <c r="AM34" t="inlineStr"/>
-      <c r="AN34" t="inlineStr"/>
-      <c r="AO34" t="inlineStr"/>
       <c r="AP34" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -20549,7 +19112,6 @@
       <c r="C35" t="n">
         <v>1</v>
       </c>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>N</t>
@@ -20560,7 +19122,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>7.6019</v>
       </c>
@@ -20651,10 +19212,6 @@
       <c r="AK35" t="n">
         <v>0.033</v>
       </c>
-      <c r="AL35" t="inlineStr"/>
-      <c r="AM35" t="inlineStr"/>
-      <c r="AN35" t="inlineStr"/>
-      <c r="AO35" t="inlineStr"/>
       <c r="AP35" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -20673,7 +19230,6 @@
       <c r="C36" t="n">
         <v>1</v>
       </c>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>N</t>
@@ -20684,7 +19240,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>8.337</v>
       </c>
@@ -20775,10 +19330,6 @@
       <c r="AK36" t="n">
         <v>0.035</v>
       </c>
-      <c r="AL36" t="inlineStr"/>
-      <c r="AM36" t="inlineStr"/>
-      <c r="AN36" t="inlineStr"/>
-      <c r="AO36" t="inlineStr"/>
       <c r="AP36" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -20797,7 +19348,6 @@
       <c r="C37" t="n">
         <v>11</v>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>N</t>
@@ -20808,7 +19358,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>8.1387</v>
       </c>
@@ -20899,10 +19448,6 @@
       <c r="AK37" t="n">
         <v>0.024</v>
       </c>
-      <c r="AL37" t="inlineStr"/>
-      <c r="AM37" t="inlineStr"/>
-      <c r="AN37" t="inlineStr"/>
-      <c r="AO37" t="inlineStr"/>
       <c r="AP37" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -20921,7 +19466,6 @@
       <c r="C38" t="n">
         <v>1</v>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>N</t>
@@ -20932,7 +19476,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>8.307499999999999</v>
       </c>
@@ -21023,10 +19566,6 @@
       <c r="AK38" t="n">
         <v>0.032</v>
       </c>
-      <c r="AL38" t="inlineStr"/>
-      <c r="AM38" t="inlineStr"/>
-      <c r="AN38" t="inlineStr"/>
-      <c r="AO38" t="inlineStr"/>
       <c r="AP38" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
@@ -21045,7 +19584,6 @@
       <c r="C39" t="n">
         <v>1</v>
       </c>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>N</t>
@@ -21056,7 +19594,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>8.798</v>
       </c>
@@ -21147,10 +19684,6 @@
       <c r="AK39" t="n">
         <v>0.036</v>
       </c>
-      <c r="AL39" t="inlineStr"/>
-      <c r="AM39" t="inlineStr"/>
-      <c r="AN39" t="inlineStr"/>
-      <c r="AO39" t="inlineStr"/>
       <c r="AP39" t="inlineStr">
         <is>
           <t>excluded-scope descriptors, computed separately (stored-table pipeline, not from SMILES)</t>
